--- a/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
+++ b/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD MRN Cube</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 18/05/2026]</t>
+    <t xml:space="preserve">[As on date 23/05/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">November</t>

--- a/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
+++ b/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD MRN Cube</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 23/05/2026]</t>
+    <t xml:space="preserve">[As on date 27/05/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">November</t>

--- a/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
+++ b/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD MRN Cube</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 04/06/2026]</t>
+    <t xml:space="preserve">[As on date 06/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">November</t>

--- a/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
+++ b/autoIt/ExportFiles/RDMRNCubeHomeExcel.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD MRN Cube</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 06/06/2026]</t>
+    <t xml:space="preserve">[As on date 22/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">November</t>
